--- a/out/LSTM-S4_repeat_2_000008.xlsx
+++ b/out/LSTM-S4_repeat_2_000008.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.734013026559911</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.734013026559911</v>
+        <v>10.67907012395075</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.066793665939915</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.666793665939915</v>
+        <v>0.1214785345699065</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001243331056493335</v>
+        <v>-8.908517028472852e-05</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1428348580168683</v>
+        <v>-0.1023417502729988</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1024308354432835</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1430679579903733</v>
+        <v>-0.1025097581408063</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3911008861765742</v>
+        <v>0.2837880463890378</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.639884742385858</v>
+        <v>0.4656112180782985</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02786585602613385</v>
+        <v>0.02021983872223807</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3038881995123101</v>
+        <v>0.2218076219583314</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04886721698434882</v>
+        <v>0.03545857947315587</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3737474779716407</v>
+        <v>0.272498451292105</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05936789746345646</v>
+        <v>0.04307829822141423</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.443611406172588</v>
+        <v>0.3231928376953367</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01571023314321541</v>
+        <v>0.0113993390061749</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4155881779095915</v>
+        <v>0.3028586413121533</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008726934056674877</v>
+        <v>0.006331256169607655</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4173179418837316</v>
+        <v>0.3041124318635659</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01833833771328134</v>
+        <v>0.01330510269712677</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.066793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4452778432230844</v>
+        <v>0.3243998215040392</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007200888064671259</v>
+        <v>0.005224415909789999</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4413270707076515</v>
+        <v>0.32153155804156</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005126682027140693</v>
+        <v>0.003719134956839246</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4443770587133849</v>
+        <v>0.3237432331153297</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002015542103882245</v>
+        <v>0.001460164603554397</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4432757407348107</v>
+        <v>0.3229428877413782</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001141811396255045</v>
+        <v>0.0008273631101851133</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.443542644037745</v>
+        <v>0.3231352369128624</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004318653538136005</v>
+        <v>0.0003120796922840649</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4432636465657349</v>
+        <v>0.3229313677799522</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000199778642475408</v>
+        <v>0.0001436296598611833</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4432310277459219</v>
+        <v>0.322906321862346</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.008125237491961e-05</v>
+        <v>4.909079472171628e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4431712398281945</v>
+        <v>0.3228615570089519</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.69413445763141e-05</v>
+        <v>1.121751555640607e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4431354470870048</v>
+        <v>0.3228340416141267</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>3.108757778203038e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4431304299602378</v>
+        <v>0.3228290289552121</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>-8.904788376657899e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.443126302459159</v>
+        <v>0.3228246473696513</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.211151546177397e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4431235013132813</v>
+        <v>0.3228212970148586</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4431180575682749</v>
+        <v>0.3228159276878708</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4431120648348446</v>
+        <v>0.3228099349544404</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4431066970462662</v>
+        <v>0.3228045671658621</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4431067337947578</v>
+        <v>0.3228046039143538</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4431068440402334</v>
+        <v>0.3228047141598293</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.443106917537217</v>
+        <v>0.3228047876568129</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4431071012796762</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4431086447163327</v>
+        <v>0.3228065148359286</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4431101146560057</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4431113641047277</v>
+        <v>0.3228092342243237</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4431127237989251</v>
+        <v>0.322810593918521</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4431105188894158</v>
+        <v>0.3228083890090117</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4431101146560057</v>
+        <v>0.3228079847756016</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.443109820668071</v>
+        <v>0.322807690787667</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4431094899316446</v>
+        <v>0.3228073600512406</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4431091959437102</v>
+        <v>0.3228070660633061</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4431088284587918</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4431087182133163</v>
+        <v>0.3228065883329122</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4431086814648246</v>
+        <v>0.3228065515844205</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4431088284587918</v>
+        <v>0.3228066985783877</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4431083507283982</v>
+        <v>0.3228062208479941</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4431093061891855</v>
+        <v>0.3228071763087814</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.3228071395602897</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4431089387042674</v>
+        <v>0.3228068088238633</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4431093796861693</v>
+        <v>0.3228072498057653</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4431087549618082</v>
+        <v>0.3228066250814041</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.443108571219349</v>
+        <v>0.3228064413389449</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.443108166985939</v>
+        <v>0.3228060371055349</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4431073217706271</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4431072850221354</v>
+        <v>0.3228051551417312</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4431074320161026</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.443107358519119</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4431074320161026</v>
+        <v>0.3228053021356985</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4431074687645945</v>
+        <v>0.3228053388841904</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.443107358519119</v>
+        <v>0.3228052286387149</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4431077995010209</v>
+        <v>0.3228056696206169</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4431076892555454</v>
+        <v>0.3228055593751413</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4431076525070535</v>
+        <v>0.3228055226266494</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4431075790100699</v>
+        <v>0.3228054491296657</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4431075422615782</v>
+        <v>0.3228054123811741</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4431073217706271</v>
+        <v>0.3228051918902229</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4431072482736435</v>
+        <v>0.3228051183932393</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4431071747766598</v>
+        <v>0.3228050448962557</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4431072115251518</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4431071012796762</v>
+        <v>0.3228049713992721</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4431072115251518</v>
+        <v>0.3228050816447476</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.4785214654300935</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4431075055130862</v>
+        <v>0.3228053756326821</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_2_000008.xlsx
+++ b/out/LSTM-S4_repeat_2_000008.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554072</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>1</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>1</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.666793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>1</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.066793665939915</v>
+        <v>1.097229942358799</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>1</v>
       </c>
       <c r="JB22" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>1</v>
       </c>
       <c r="JB23" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>1</v>
       </c>
       <c r="JB24" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>1</v>
       </c>
       <c r="JB33" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>1</v>
       </c>
       <c r="JB36" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>1</v>
       </c>
       <c r="JB37" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001243331056493335</v>
+        <v>-0.0001204656295455061</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1428348580168683</v>
+        <v>-0.1383918707908722</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="49">
@@ -39899,10 +39899,10 @@
         <v>1</v>
       </c>
       <c r="JB49" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="50">
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="51">
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="52">
@@ -42284,10 +42284,10 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="53">
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="54">
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="55">
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="56">
@@ -45464,10 +45464,10 @@
         <v>1</v>
       </c>
       <c r="JB56" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="57">
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="58">
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1429591911225176</v>
+        <v>-0.1385123364204178</v>
       </c>
     </row>
     <row r="59">
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1430679579903733</v>
+        <v>-0.1386179828641018</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3911008861765742</v>
+        <v>0.3798805515024933</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.639884742385858</v>
+        <v>0.6218725047105188</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.02786585602613385</v>
+        <v>0.0270663729501157</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>1</v>
       </c>
       <c r="JB61" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.3038881995123101</v>
+        <v>0.2955154023421509</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04886721698434882</v>
+        <v>0.04746519606977675</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3737474779716407</v>
+        <v>0.3633705725968818</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05936789746345646</v>
+        <v>0.05766491941614117</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.443611406172588</v>
+        <v>0.4312304423570081</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01571023314321541</v>
+        <v>0.01525941747038739</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.734013026559911</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4155881779095915</v>
+        <v>0.4040110654290032</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008726934056674877</v>
+        <v>0.008476726963416096</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.066793665939915</v>
+        <v>0.2570455555016958</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4173179418837316</v>
+        <v>0.4056910853327788</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01833833771328134</v>
+        <v>0.01781134741852105</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>1</v>
       </c>
       <c r="JB66" t="n">
-        <v>1.066793665939915</v>
+        <v>0.8972299423587988</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4452778432230844</v>
+        <v>0.4328486766766338</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.007200888064671259</v>
+        <v>0.006995005548537794</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>1.666793665939915</v>
+        <v>0.2570455555016957</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4413270707076515</v>
+        <v>0.4290109618055988</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.005126682027140693</v>
+        <v>0.004980062540650959</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.3831388313554074</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.4443770587133849</v>
+        <v>0.431973164660251</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.002015542103882245</v>
+        <v>0.001957152782331884</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4432757407348107</v>
+        <v>0.4309035279135844</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001141811396255045</v>
+        <v>0.001107900306580837</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.443542644037745</v>
+        <v>0.4311625748075466</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004318653538136005</v>
+        <v>0.0004189472922761016</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4432636465657349</v>
+        <v>0.4308913119264038</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.000199778642475408</v>
+        <v>0.0001942738402583272</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4432310277459219</v>
+        <v>0.4308594355479837</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>7.008125237491961e-05</v>
+        <v>6.76592764918577e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4431712398281945</v>
+        <v>0.4308011209945064</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.69413445763141e-05</v>
+        <v>1.64643588246551e-05</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4431354470870048</v>
+        <v>0.4307659904708117</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4431304299602378</v>
+        <v>0.4307609733440448</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>1.164281743501315e-06</v>
+        <v>6.505915982095382e-07</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.443126302459159</v>
+        <v>0.4307568098832141</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4431235013132813</v>
+        <v>0.4307540087373364</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4431180575682749</v>
+        <v>0.4307485649923301</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4431120648348446</v>
+        <v>0.4307425722588997</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4431066970462662</v>
+        <v>0.4307372044703213</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.4431067337947578</v>
+        <v>0.430737241218813</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4431068440402334</v>
+        <v>0.4307373514642885</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.443106917537217</v>
+        <v>0.4307374249612722</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4431071012796762</v>
+        <v>0.4307376087037313</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4431086447163327</v>
+        <v>0.4307391521403878</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4431101146560057</v>
+        <v>0.4307406220800609</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4431113641047277</v>
+        <v>0.4307418715287829</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.666793665939915</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4431127237989251</v>
+        <v>0.4307432312229802</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.1831388313554072</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4431105188894158</v>
+        <v>0.4307410263134709</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.134013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4431101146560057</v>
+        <v>0.4307406220800609</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.734013026559911</v>
+        <v>-0.8233232182125103</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.4307397768647489</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.443109820668071</v>
+        <v>0.4307403280921262</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4431094899316446</v>
+        <v>0.4307399973556998</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4431091959437102</v>
+        <v>0.4307397033677653</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.4307397768647489</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>0</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.4431088284587918</v>
+        <v>0.430739335882847</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4431087182133163</v>
+        <v>0.4307392256373714</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4431086814648246</v>
+        <v>0.4307391888888797</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.4431088284587918</v>
+        <v>0.430739335882847</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4431083507283982</v>
+        <v>0.4307388581524533</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4431093061891855</v>
+        <v>0.4307398136132406</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4431092694406938</v>
+        <v>0.4307397768647489</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4431089387042674</v>
+        <v>0.4307394461283225</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4431093796861693</v>
+        <v>0.4307398871102245</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4431087549618082</v>
+        <v>0.4307392623858634</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.443108571219349</v>
+        <v>0.4307390786434042</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.443108166985939</v>
+        <v>0.4307386744099941</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4431073217706271</v>
+        <v>0.4307378291946822</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4431072850221354</v>
+        <v>0.4307377924461905</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4431074320161026</v>
+        <v>0.4307379394401578</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.443107358519119</v>
+        <v>0.4307378659431741</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4431074320161026</v>
+        <v>0.4307379394401578</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4431074687645945</v>
+        <v>0.4307379761886497</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.443107358519119</v>
+        <v>0.4307378659431741</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4431077995010209</v>
+        <v>0.4307383069250761</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4431076892555454</v>
+        <v>0.4307381966796005</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4431076525070535</v>
+        <v>0.4307381599311086</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.4431075790100699</v>
+        <v>0.430738086434125</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4431075422615782</v>
+        <v>0.4307380496856333</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4431073217706271</v>
+        <v>0.4307378291946822</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4431072482736435</v>
+        <v>0.4307377556976986</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.4431071747766598</v>
+        <v>0.430737682200715</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4431072115251518</v>
+        <v>0.4307377189492069</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4431071012796762</v>
+        <v>0.4307376087037313</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4431072115251518</v>
+        <v>0.4307377189492069</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.734013026559911</v>
+        <v>-1.02332321821251</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4431075055130862</v>
+        <v>0.4307380129371414</v>
       </c>
     </row>
   </sheetData>

--- a/out/LSTM-S4_repeat_2_000008.xlsx
+++ b/out/LSTM-S4_repeat_2_000008.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>-0.002069300040602684</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.44</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>-0.001114161685109138</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.3831388313554072</v>
+        <v>-0.16</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4121,10 +4121,10 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.000325378030538559</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.2570455555016958</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.001430831849575043</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.097229942358799</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>1</v>
+        <v>0.001021808013319969</v>
       </c>
       <c r="JB6" t="n">
-        <v>1.097229942358799</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.0002936795353889465</v>
       </c>
       <c r="JB7" t="n">
-        <v>1.097229942358799</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>6.530247628688812e-05</v>
       </c>
       <c r="JB8" t="n">
-        <v>1.097229942358799</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>1</v>
+        <v>0.0001129694283008575</v>
       </c>
       <c r="JB9" t="n">
-        <v>1.097229942358799</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.0003293938934803009</v>
       </c>
       <c r="JB10" t="n">
-        <v>1.097229942358799</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>1</v>
+        <v>0.0005190800875425339</v>
       </c>
       <c r="JB11" t="n">
-        <v>1.097229942358799</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>1</v>
+        <v>0.0009314622730016708</v>
       </c>
       <c r="JB12" t="n">
-        <v>1.097229942358799</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>1</v>
+        <v>0.001471972092986107</v>
       </c>
       <c r="JB13" t="n">
-        <v>1.097229942358799</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.001950440928339958</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.002198193222284317</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.002665102481842041</v>
       </c>
       <c r="JB16" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.002391574904322624</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.002024991437792778</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.001858238130807877</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.001957543194293976</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.16</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.002128956839442253</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.16</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>1</v>
+        <v>0.002253752201795578</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>1</v>
+        <v>0.002564778551459312</v>
       </c>
       <c r="JB23" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>1</v>
+        <v>0.002906749024987221</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.003348805010318756</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>1</v>
+        <v>0.003514572978019714</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.003604315221309662</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.003547023981809616</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>1</v>
+        <v>0.003574628382921219</v>
       </c>
       <c r="JB29" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>1</v>
+        <v>0.00371977686882019</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.004007317125797272</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.004948940128087997</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>1</v>
+        <v>0.004734594374895096</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>1</v>
+        <v>0.004413936287164688</v>
       </c>
       <c r="JB34" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.004267385229468346</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>1</v>
+        <v>0.004074763506650925</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>1</v>
+        <v>0.004124004393815994</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.003973308950662613</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.003904823213815689</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.004425574094057083</v>
       </c>
       <c r="JB40" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.004823146387934685</v>
       </c>
       <c r="JB41" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.004929324612021446</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.005230285227298737</v>
       </c>
       <c r="JB43" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.005998123437166214</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.006335217505693436</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.8972299423587988</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC45" t="n">
-        <v>-0.0001204656295455061</v>
+        <v>-0.0001132297395697096</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1383918707908722</v>
+        <v>-0.1300792229893992</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>1</v>
+        <v>0.004737526178359985</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.003484416753053665</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC47" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.002098621800541878</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="49">
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>1</v>
+        <v>0.001473542302846909</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="50">
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.001187806949019432</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="51">
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.001155639067292213</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC51" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="52">
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.001391813158988953</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC52" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="53">
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.00198911689221859</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC53" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="54">
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.002302469685673714</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC54" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="55">
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.002512287348508835</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC55" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="56">
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>1</v>
+        <v>0.002363795414566994</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="57">
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.002074543386697769</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="58">
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.001921519637107849</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>-0.1385123364204178</v>
+        <v>-0.1301924527289689</v>
       </c>
     </row>
     <row r="59">
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.002407966181635857</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>-0.1386179828641018</v>
+        <v>-0.1302574926734896</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.3798805515024933</v>
+        <v>0.2338688282598552</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.001805216073989868</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6218725047105188</v>
+        <v>0.3379292005604627</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.0270663729501157</v>
+        <v>0.01666306832510367</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>1</v>
+        <v>0.00126129575073719</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.2955154023421509</v>
+        <v>0.1370114310152538</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.04746519606977675</v>
+        <v>0.02922147270272843</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.001294907182455063</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.3633705725968818</v>
+        <v>0.1787856740458205</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.05766491941614117</v>
+        <v>0.03550063830527529</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.000711686909198761</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.4312304423570081</v>
+        <v>0.220562697515015</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.01525941747038739</v>
+        <v>0.009393237161945765</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>-0.0002658311277627945</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.4040110654290032</v>
+        <v>0.2038044951955106</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.008476726963416096</v>
+        <v>0.005216697299636718</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.0004789363592863083</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.2570455555016958</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.4056910853327788</v>
+        <v>0.2048368622222175</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>0.01781134741852105</v>
+        <v>0.01096369609643938</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>1</v>
+        <v>0.001040080562233925</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.8972299423587988</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.4328486766766338</v>
+        <v>0.2215547841622636</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>0.006995005548537794</v>
+        <v>0.004303999955310981</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.000716356560587883</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.2570455555016957</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.4290109618055988</v>
+        <v>0.2191901455519372</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>0.004980062540650959</v>
+        <v>0.003063659605473376</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>-0.0004219003021717072</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.3831388313554074</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.431973164660251</v>
+        <v>0.2210121838641879</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>0.001957152782331884</v>
+        <v>0.001203523166972579</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>-0.001139873638749123</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.4309035279135844</v>
+        <v>0.2203514560409817</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>0.001107900306580837</v>
+        <v>0.0006809288593192138</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>-0.002076040953397751</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.4311625748075466</v>
+        <v>0.220509086376742</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>0.0004189472922761016</v>
+        <v>0.0002557099692113423</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>-0.003046911209821701</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.4308913119264038</v>
+        <v>0.2203402042714309</v>
       </c>
     </row>
     <row r="72">
@@ -58173,7 +58173,7 @@
         <v>0</v>
       </c>
       <c r="IY72" t="n">
-        <v>0.0001942738402583272</v>
+        <v>0.0001172066092191951</v>
       </c>
       <c r="IZ72" t="inlineStr">
         <is>
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>-0.003940446302294731</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.4308594355479837</v>
+        <v>0.2203186485755267</v>
       </c>
     </row>
     <row r="73">
@@ -58968,7 +58968,7 @@
         <v>0</v>
       </c>
       <c r="IY73" t="n">
-        <v>6.76592764918577e-05</v>
+        <v>4.021021648382256e-05</v>
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>-0.004539201036095619</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.4308011209945064</v>
+        <v>0.220280658001411</v>
       </c>
     </row>
     <row r="74">
@@ -59763,7 +59763,7 @@
         <v>0</v>
       </c>
       <c r="IY74" t="n">
-        <v>1.64643588246551e-05</v>
+        <v>8.355601046452064e-06</v>
       </c>
       <c r="IZ74" t="inlineStr">
         <is>
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>-0.004584040492773056</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.4307659904708117</v>
+        <v>0.2202571159115553</v>
       </c>
     </row>
     <row r="75">
@@ -60558,7 +60558,7 @@
         <v>0</v>
       </c>
       <c r="IY75" t="n">
-        <v>5.970672288157051e-06</v>
+        <v>1.677800523226032e-06</v>
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>-0.004444556310772896</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.4307609733440448</v>
+        <v>0.2202521054865667</v>
       </c>
     </row>
     <row r="76">
@@ -61353,7 +61353,7 @@
         <v>0</v>
       </c>
       <c r="IY76" t="n">
-        <v>6.505915982095382e-07</v>
+        <v>-1.404168982957566e-06</v>
       </c>
       <c r="IZ76" t="inlineStr">
         <is>
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>-0.004103133454918861</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.4307568098832141</v>
+        <v>0.2202476144442705</v>
       </c>
     </row>
     <row r="77">
@@ -62148,7 +62148,7 @@
         <v>0</v>
       </c>
       <c r="IY77" t="n">
-        <v>-8.167273192660964e-07</v>
+        <v>-2.908363659633048e-06</v>
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>-0.004202377051115036</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.4307540087373364</v>
+        <v>0.2202438976137908</v>
       </c>
     </row>
     <row r="78">
@@ -62943,7 +62943,7 @@
         <v>0</v>
       </c>
       <c r="IY78" t="n">
-        <v>-3.128590021429696e-06</v>
+        <v>-3.752393347619798e-06</v>
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>-0.004577541723847389</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.4307485649923301</v>
+        <v>0.2202386017837867</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>-0.004951128736138344</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.4307425722588997</v>
+        <v>0.220232939786783</v>
       </c>
     </row>
     <row r="80">
@@ -64533,7 +64533,7 @@
         <v>0</v>
       </c>
       <c r="IY80" t="n">
-        <v>-4.890058184668745e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>-0.005058297887444496</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.4307372044703213</v>
+        <v>0.2202327560443238</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>-0.005062643438577652</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.430737241218813</v>
+        <v>0.2202327927928155</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>-0.004841480404138565</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.4307373514642885</v>
+        <v>0.220232903038291</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>-0.004547802731394768</v>
       </c>
       <c r="JB83" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.4307374249612722</v>
+        <v>0.2202329765352747</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>-0.003525175154209137</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.4307376087037313</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>-0.001790471374988556</v>
       </c>
       <c r="JB85" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.3</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.4307391521403878</v>
+        <v>0.2202347037143903</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>-0.001388991251587868</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.4307406220800609</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>-0.001483961939811707</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.4307418715287829</v>
+        <v>0.2202374231027854</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.0001093782484531403</v>
       </c>
       <c r="JB88" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.4307432312229802</v>
+        <v>0.2202387827969827</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>-0.001962488517165184</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.1831388313554072</v>
+        <v>0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.4307410263134709</v>
+        <v>0.2202365778874734</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>-0.004835912957787514</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.8233232182125103</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.4307406220800609</v>
+        <v>0.2202361736540634</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>-0.007078120484948158</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.8233232182125103</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.4307397768647489</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>-0.008548030629754066</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.4307403280921262</v>
+        <v>0.2202358796661286</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>-0.009741669520735741</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.4307399973556998</v>
+        <v>0.2202355489297023</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>-0.01010949909687042</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.4307397033677653</v>
+        <v>0.2202352549417678</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>-0.01015056669712067</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.4307397768647489</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0</v>
+        <v>-0.009589022025465965</v>
       </c>
       <c r="JB96" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.430739335882847</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>-0.0090042594820261</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.4307392256373714</v>
+        <v>0.2202347772113739</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>-0.008288359269499779</v>
       </c>
       <c r="JB98" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.4307391888888797</v>
+        <v>0.2202347404628822</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>-0.008200161159038544</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.430739335882847</v>
+        <v>0.2202348874568494</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>-0.00741446390748024</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.4307388581524533</v>
+        <v>0.2202344097264558</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>-0.007055124267935753</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.4307398136132406</v>
+        <v>0.2202353651872431</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>-0.008604846894741058</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.4307397768647489</v>
+        <v>0.2202353284387514</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>-0.009969986975193024</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.4307394461283225</v>
+        <v>0.220234997702325</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>-0.01119763776659966</v>
       </c>
       <c r="JB104" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.4307398871102245</v>
+        <v>0.220235438684227</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>-0.01187143567949533</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.4307392623858634</v>
+        <v>0.2202348139598658</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>-0.01220723893493414</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.4307390786434042</v>
+        <v>0.2202346302174067</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>-0.01255413517355919</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.4307386744099941</v>
+        <v>0.2202342259839966</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>-0.01207202672958374</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.4307378291946822</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>-0.01105009950697422</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.4307377924461905</v>
+        <v>0.220233344020193</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>-0.01000685431063175</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.2599999999999998</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.4307379394401578</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>-0.008831683546304703</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.4307378659431741</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>-0.007432339712977409</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.3</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.4307379394401578</v>
+        <v>0.2202334910141602</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>-0.007509941235184669</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.4307379761886497</v>
+        <v>0.2202335277626521</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>-0.006974639371037483</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.4307378659431741</v>
+        <v>0.2202334175171766</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>-0.006730429828166962</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.4307383069250761</v>
+        <v>0.2202338584990785</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>-0.00682375393807888</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.4307381966796005</v>
+        <v>0.220233748253603</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>-0.007216311991214752</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.4307381599311086</v>
+        <v>0.2202337115051111</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>-0.006944829598069191</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.430738086434125</v>
+        <v>0.2202336380081275</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>-0.006980244070291519</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.4307380496856333</v>
+        <v>0.2202336012596358</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>-0.007219962775707245</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.4307378291946822</v>
+        <v>0.2202333807686847</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>-0.006832676008343697</v>
       </c>
       <c r="JB121" t="n">
-        <v>-1.02332321821251</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.4307377556976986</v>
+        <v>0.220233307271701</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>-0.006508544087409973</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.1199999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.430737682200715</v>
+        <v>0.2202332337747174</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>-0.006394706666469574</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.2599999999999998</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.4307377189492069</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>-0.005865469574928284</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.4307376087037313</v>
+        <v>0.2202331602777338</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>-0.004761273041367531</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.4307377189492069</v>
+        <v>0.2202332705232093</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>-0.00430307537317276</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.02332321821251</v>
+        <v>0.9999999999999996</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.4307380129371414</v>
+        <v>0.2202335645111438</v>
       </c>
     </row>
   </sheetData>
